--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="539">
   <si>
     <t>key</t>
   </si>
@@ -116,6 +116,13 @@
   <si>
     <t>一打一（我是房主）
 &lt;size=12&gt;其他玩家可加入您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>YiDaYi_PvE</t>
+  </si>
+  <si>
+    <t>一打一（打电脑）
+&lt;size=12&gt;其他玩家可旁观您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
   </si>
   <si>
     <t>ZhongYangFangShou_WanJiaHeZuo</t>
@@ -1852,7 +1859,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1873,6 +1880,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -2428,148 +2441,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2585,33 +2598,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2620,28 +2633,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3027,7 +3040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="68.625" customWidth="1"/>
@@ -3189,7 +3202,7 @@
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -3211,7 +3224,7 @@
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="28.5" spans="1:3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -3221,14 +3234,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:3">
-      <c r="A18" s="2" t="s">
+    <row r="18" s="2" customFormat="1" ht="28.5" spans="1:3">
+      <c r="A18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3291,10 +3304,10 @@
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="2" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3302,10 +3315,10 @@
       <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3331,25 +3344,25 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" spans="1:3">
-      <c r="A28" s="3" t="s">
+    <row r="28" s="2" customFormat="1" spans="1:3">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:3">
-      <c r="A29" s="2" t="s">
+    <row r="29" s="3" customFormat="1" spans="1:3">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="9" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3375,80 +3388,80 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" ht="215.25" spans="1:3">
+    <row r="32" s="2" customFormat="1" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" spans="1:3">
+    <row r="33" s="2" customFormat="1" ht="215.25" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" ht="28.5" spans="1:3">
-      <c r="A34" s="6" t="s">
+    <row r="34" s="2" customFormat="1" spans="1:3">
+      <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" ht="28.5" spans="1:3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" s="4" customFormat="1" spans="1:3">
-      <c r="A37" s="10" t="s">
+    <row r="37" ht="28.5" spans="1:3">
+      <c r="A37" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3456,37 +3469,37 @@
       <c r="A39" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:3">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="1" ht="17.25" spans="1:3">
-      <c r="A41" s="12" t="s">
+    <row r="41" s="4" customFormat="1" spans="1:3">
+      <c r="A41" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" ht="17.25" spans="1:3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -3500,21 +3513,21 @@
       <c r="A43" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" s="4" customFormat="1" spans="1:3">
+    <row r="44" s="4" customFormat="1" ht="17.25" spans="1:3">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="14" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3522,10 +3535,10 @@
       <c r="A45" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3533,10 +3546,10 @@
       <c r="A46" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3544,10 +3557,10 @@
       <c r="A47" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3555,10 +3568,10 @@
       <c r="A48" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3566,10 +3579,10 @@
       <c r="A49" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3577,10 +3590,10 @@
       <c r="A50" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3588,10 +3601,10 @@
       <c r="A51" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3599,10 +3612,10 @@
       <c r="A52" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3610,10 +3623,10 @@
       <c r="A53" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3621,10 +3634,10 @@
       <c r="A54" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3632,10 +3645,10 @@
       <c r="A55" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3643,10 +3656,10 @@
       <c r="A56" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3654,26 +3667,26 @@
       <c r="A57" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="6" t="s">
+    <row r="58" s="4" customFormat="1" spans="1:3">
+      <c r="A58" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="7" t="s">
         <v>116</v>
       </c>
       <c r="B59" t="s">
@@ -3684,7 +3697,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="7" t="s">
         <v>118</v>
       </c>
       <c r="B60" t="s">
@@ -3695,7 +3708,7 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" t="s">
+      <c r="A61" s="7" t="s">
         <v>120</v>
       </c>
       <c r="B61" t="s">
@@ -3969,47 +3982,47 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" ht="42.75" spans="1:3">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" ht="42.75" spans="1:3">
       <c r="A87" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="88" ht="28.5" spans="1:3">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="10" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" ht="28.5" spans="1:3">
       <c r="A89" t="s">
         <v>176</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="10" t="s">
         <v>177</v>
       </c>
     </row>
@@ -4167,14 +4180,14 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" ht="28.5" spans="1:3">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>206</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C104" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4182,48 +4195,48 @@
       <c r="A105" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C105" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" ht="28.5" spans="1:3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="10" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="107" ht="28.5" spans="1:3">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>212</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="9" t="s">
+      <c r="C107" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="6" t="s">
+    <row r="108" ht="28.5" spans="1:3">
+      <c r="A108" t="s">
         <v>214</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="10" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="7" t="s">
         <v>216</v>
       </c>
       <c r="B109" t="s">
@@ -4234,7 +4247,7 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="7" t="s">
         <v>218</v>
       </c>
       <c r="B110" t="s">
@@ -4245,35 +4258,35 @@
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" t="s">
         <v>221</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="7" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" t="s">
+      <c r="A113" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="7" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4332,29 +4345,29 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" ht="28.5" spans="1:3">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" t="s">
         <v>237</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="C119" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="120" customFormat="1" spans="1:3">
+    <row r="120" ht="28.5" spans="1:3">
       <c r="A120" t="s">
         <v>238</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" customFormat="1" spans="1:3">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -4365,7 +4378,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" customFormat="1" spans="1:3">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>242</v>
       </c>
@@ -4376,51 +4389,51 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" ht="28.5" spans="1:3">
+    <row r="123" customFormat="1" spans="1:3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
-      <c r="B123" s="9" t="s">
+      <c r="B123" t="s">
         <v>245</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="124" customFormat="1" spans="1:3">
+    <row r="124" ht="28.5" spans="1:3">
       <c r="A124" t="s">
         <v>246</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="10" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="125" ht="28.5" spans="1:3">
+    <row r="125" customFormat="1" spans="1:3">
       <c r="A125" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" t="s">
         <v>249</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" customFormat="1" spans="1:3">
+    <row r="126" ht="28.5" spans="1:3">
       <c r="A126" t="s">
         <v>250</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" customFormat="1" spans="1:3">
       <c r="A127" t="s">
         <v>252</v>
       </c>
@@ -4431,7 +4444,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" customFormat="1" spans="1:3">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>254</v>
       </c>
@@ -4442,7 +4455,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" customFormat="1" spans="1:3">
       <c r="A129" t="s">
         <v>256</v>
       </c>
@@ -4453,7 +4466,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" customFormat="1" spans="1:3">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>258</v>
       </c>
@@ -4464,124 +4477,124 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" ht="28.5" spans="1:3">
+    <row r="131" customFormat="1" spans="1:3">
       <c r="A131" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="9" t="s">
+      <c r="B131" t="s">
         <v>261</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="132" customFormat="1" spans="1:3">
+    <row r="132" ht="28.5" spans="1:3">
       <c r="A132" t="s">
         <v>262</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="133" ht="28.5" spans="1:3">
+    <row r="133" customFormat="1" spans="1:3">
       <c r="A133" t="s">
         <v>264</v>
       </c>
-      <c r="B133" s="9" t="s">
+      <c r="B133" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="134" customFormat="1" spans="1:3">
+    <row r="134" ht="28.5" spans="1:3">
       <c r="A134" t="s">
         <v>266</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="10" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="135" ht="28.5" spans="1:3">
+    <row r="135" customFormat="1" spans="1:3">
       <c r="A135" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B135" t="s">
         <v>269</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="136" customFormat="1" spans="1:3">
+    <row r="136" ht="28.5" spans="1:3">
       <c r="A136" t="s">
         <v>270</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" customFormat="1" spans="1:3">
+      <c r="A137" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="137" ht="28.5" spans="1:3">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>273</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="C137" t="s">
         <v>274</v>
       </c>
-      <c r="C137" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="138" customFormat="1" spans="1:3">
+    </row>
+    <row r="138" ht="28.5" spans="1:3">
       <c r="A138" t="s">
         <v>275</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="10" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="139" ht="28.5" spans="1:3">
+    <row r="139" customFormat="1" spans="1:3">
       <c r="A139" t="s">
         <v>277</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" t="s">
         <v>278</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="140" customFormat="1" spans="1:3">
+    <row r="140" ht="28.5" spans="1:3">
       <c r="A140" t="s">
         <v>279</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="141" ht="42.75" spans="1:3">
+    <row r="141" customFormat="1" spans="1:3">
       <c r="A141" t="s">
         <v>281</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B141" t="s">
         <v>282</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4589,10 +4602,10 @@
       <c r="A142" t="s">
         <v>283</v>
       </c>
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="10" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4600,10 +4613,10 @@
       <c r="A143" t="s">
         <v>285</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="10" t="s">
         <v>286</v>
       </c>
     </row>
@@ -4611,10 +4624,10 @@
       <c r="A144" t="s">
         <v>287</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="10" t="s">
         <v>288</v>
       </c>
     </row>
@@ -4622,10 +4635,10 @@
       <c r="A145" t="s">
         <v>289</v>
       </c>
-      <c r="B145" s="9" t="s">
+      <c r="B145" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="10" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4633,10 +4646,10 @@
       <c r="A146" t="s">
         <v>291</v>
       </c>
-      <c r="B146" s="9" t="s">
+      <c r="B146" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="10" t="s">
         <v>292</v>
       </c>
     </row>
@@ -4644,10 +4657,10 @@
       <c r="A147" t="s">
         <v>293</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="10" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4655,58 +4668,58 @@
       <c r="A148" t="s">
         <v>295</v>
       </c>
-      <c r="B148" s="9" t="s">
+      <c r="B148" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="149" ht="28.5" spans="1:3">
+    <row r="149" ht="42.75" spans="1:3">
       <c r="A149" t="s">
         <v>297</v>
       </c>
-      <c r="B149" s="9" t="s">
+      <c r="B149" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="150" customFormat="1" spans="1:3">
+    <row r="150" ht="28.5" spans="1:3">
       <c r="A150" t="s">
         <v>299</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="151" ht="28.5" spans="1:3">
+    <row r="151" customFormat="1" spans="1:3">
       <c r="A151" t="s">
         <v>301</v>
       </c>
-      <c r="B151" s="9" t="s">
+      <c r="B151" t="s">
         <v>302</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="152" customFormat="1" spans="1:3">
+    <row r="152" ht="28.5" spans="1:3">
       <c r="A152" t="s">
         <v>303</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="10" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" customFormat="1" spans="1:3">
       <c r="A153" t="s">
         <v>305</v>
       </c>
@@ -4721,10 +4734,10 @@
       <c r="A154" t="s">
         <v>307</v>
       </c>
-      <c r="B154" s="15" t="s">
+      <c r="B154" t="s">
         <v>308</v>
       </c>
-      <c r="C154" s="15" t="s">
+      <c r="C154" t="s">
         <v>308</v>
       </c>
     </row>
@@ -4732,10 +4745,10 @@
       <c r="A155" t="s">
         <v>309</v>
       </c>
-      <c r="B155" s="15" t="s">
+      <c r="B155" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="C155" s="15" t="s">
+      <c r="C155" s="16" t="s">
         <v>310</v>
       </c>
     </row>
@@ -4743,10 +4756,10 @@
       <c r="A156" t="s">
         <v>311</v>
       </c>
-      <c r="B156" s="15" t="s">
+      <c r="B156" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="C156" s="15" t="s">
+      <c r="C156" s="16" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4754,10 +4767,10 @@
       <c r="A157" t="s">
         <v>313</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B157" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="16" t="s">
         <v>314</v>
       </c>
     </row>
@@ -4765,10 +4778,10 @@
       <c r="A158" t="s">
         <v>315</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B158" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="7" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4776,10 +4789,10 @@
       <c r="A159" t="s">
         <v>317</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C159" s="7" t="s">
         <v>318</v>
       </c>
     </row>
@@ -4787,10 +4800,10 @@
       <c r="A160" t="s">
         <v>319</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C160" s="7" t="s">
         <v>320</v>
       </c>
     </row>
@@ -4798,10 +4811,10 @@
       <c r="A161" t="s">
         <v>321</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B161" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C161" s="7" t="s">
         <v>322</v>
       </c>
     </row>
@@ -4809,10 +4822,10 @@
       <c r="A162" t="s">
         <v>323</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B162" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C162" s="7" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4820,10 +4833,10 @@
       <c r="A163" t="s">
         <v>325</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C163" s="16" t="s">
+      <c r="C163" s="7" t="s">
         <v>326</v>
       </c>
     </row>
@@ -4853,10 +4866,10 @@
       <c r="A166" t="s">
         <v>331</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B166" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C166" s="19" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4864,10 +4877,10 @@
       <c r="A167" t="s">
         <v>333</v>
       </c>
-      <c r="B167" s="17" t="s">
+      <c r="B167" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C167" s="18" t="s">
         <v>334</v>
       </c>
     </row>
@@ -4875,10 +4888,10 @@
       <c r="A168" t="s">
         <v>335</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B168" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C168" s="18" t="s">
         <v>336</v>
       </c>
     </row>
@@ -4886,10 +4899,10 @@
       <c r="A169" t="s">
         <v>337</v>
       </c>
-      <c r="B169" s="17" t="s">
+      <c r="B169" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="C169" s="17" t="s">
+      <c r="C169" s="18" t="s">
         <v>338</v>
       </c>
     </row>
@@ -4897,43 +4910,43 @@
       <c r="A170" t="s">
         <v>339</v>
       </c>
-      <c r="B170" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="C170" s="17" t="s">
-        <v>330</v>
+      <c r="B170" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" s="18" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>340</v>
-      </c>
-      <c r="B171" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B171" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="C171" s="17" t="s">
+      <c r="C171" s="18" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>341</v>
-      </c>
-      <c r="B172" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C172" s="17" t="s">
-        <v>342</v>
+      <c r="B172" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C172" s="18" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>343</v>
       </c>
-      <c r="B173" s="17" t="s">
+      <c r="B173" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="C173" s="17" t="s">
+      <c r="C173" s="18" t="s">
         <v>344</v>
       </c>
     </row>
@@ -4941,10 +4954,10 @@
       <c r="A174" t="s">
         <v>345</v>
       </c>
-      <c r="B174" s="17" t="s">
+      <c r="B174" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="C174" s="17" t="s">
+      <c r="C174" s="18" t="s">
         <v>346</v>
       </c>
     </row>
@@ -4952,10 +4965,10 @@
       <c r="A175" t="s">
         <v>347</v>
       </c>
-      <c r="B175" s="17" t="s">
+      <c r="B175" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="C175" s="17" t="s">
+      <c r="C175" s="18" t="s">
         <v>348</v>
       </c>
     </row>
@@ -4963,10 +4976,10 @@
       <c r="A176" t="s">
         <v>349</v>
       </c>
-      <c r="B176" s="17" t="s">
+      <c r="B176" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C176" s="17" t="s">
+      <c r="C176" s="18" t="s">
         <v>350</v>
       </c>
     </row>
@@ -4974,10 +4987,10 @@
       <c r="A177" t="s">
         <v>351</v>
       </c>
-      <c r="B177" s="17" t="s">
+      <c r="B177" s="18" t="s">
         <v>352</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C177" s="18" t="s">
         <v>352</v>
       </c>
     </row>
@@ -4985,10 +4998,10 @@
       <c r="A178" t="s">
         <v>353</v>
       </c>
-      <c r="B178" s="16" t="s">
+      <c r="B178" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="C178" s="16" t="s">
+      <c r="C178" s="18" t="s">
         <v>354</v>
       </c>
     </row>
@@ -4996,10 +5009,10 @@
       <c r="A179" t="s">
         <v>355</v>
       </c>
-      <c r="B179" s="16" t="s">
+      <c r="B179" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="C179" s="16" t="s">
+      <c r="C179" s="17" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5007,32 +5020,32 @@
       <c r="A180" t="s">
         <v>357</v>
       </c>
-      <c r="B180" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="C180" s="16" t="s">
-        <v>346</v>
+      <c r="B180" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>358</v>
-      </c>
-      <c r="B181" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="C181" s="16" t="s">
-        <v>359</v>
+      <c r="B181" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="C181" s="17" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
         <v>360</v>
       </c>
-      <c r="B182" s="16" t="s">
+      <c r="B182" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="C182" s="16" t="s">
+      <c r="C182" s="17" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5040,10 +5053,10 @@
       <c r="A183" t="s">
         <v>362</v>
       </c>
-      <c r="B183" s="16" t="s">
+      <c r="B183" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C183" s="16" t="s">
+      <c r="C183" s="17" t="s">
         <v>363</v>
       </c>
     </row>
@@ -5051,10 +5064,10 @@
       <c r="A184" t="s">
         <v>364</v>
       </c>
-      <c r="B184" s="16" t="s">
+      <c r="B184" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C184" s="16" t="s">
+      <c r="C184" s="17" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5062,10 +5075,10 @@
       <c r="A185" t="s">
         <v>366</v>
       </c>
-      <c r="B185" s="16" t="s">
+      <c r="B185" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C185" s="16" t="s">
+      <c r="C185" s="17" t="s">
         <v>367</v>
       </c>
     </row>
@@ -5073,10 +5086,10 @@
       <c r="A186" t="s">
         <v>368</v>
       </c>
-      <c r="B186" s="16" t="s">
+      <c r="B186" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C186" s="16" t="s">
+      <c r="C186" s="17" t="s">
         <v>369</v>
       </c>
     </row>
@@ -5084,10 +5097,10 @@
       <c r="A187" t="s">
         <v>370</v>
       </c>
-      <c r="B187" s="16" t="s">
+      <c r="B187" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C187" s="16" t="s">
+      <c r="C187" s="17" t="s">
         <v>371</v>
       </c>
     </row>
@@ -5095,10 +5108,10 @@
       <c r="A188" t="s">
         <v>372</v>
       </c>
-      <c r="B188" s="16" t="s">
+      <c r="B188" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C188" s="16" t="s">
+      <c r="C188" s="17" t="s">
         <v>373</v>
       </c>
     </row>
@@ -5106,32 +5119,32 @@
       <c r="A189" t="s">
         <v>374</v>
       </c>
-      <c r="B189" s="16" t="s">
+      <c r="B189" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="C189" s="16" t="s">
+      <c r="C189" s="17" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="19" t="s">
+      <c r="A190" t="s">
         <v>376</v>
       </c>
-      <c r="B190" s="19" t="s">
+      <c r="B190" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C190" s="19" t="s">
+      <c r="C190" s="17" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="19" t="s">
+      <c r="A191" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="B191" s="19" t="s">
+      <c r="B191" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="19" t="s">
+      <c r="C191" s="20" t="s">
         <v>379</v>
       </c>
     </row>
@@ -5147,47 +5160,47 @@
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="20" t="s">
+      <c r="A193" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="B193" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C193" s="20" t="s">
-        <v>199</v>
+      <c r="B193" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="C193" s="21" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="B195" s="21" t="s">
+      <c r="A195" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="B195" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C195" s="21" t="s">
+      <c r="C195" s="22" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>386</v>
+        <v>221</v>
       </c>
       <c r="C196" s="22" t="s">
-        <v>386</v>
+        <v>221</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -5202,310 +5215,310 @@
       </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="22" t="s">
+      <c r="A198" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="B198" s="22" t="s">
+      <c r="B198" s="24" t="s">
         <v>390</v>
       </c>
-      <c r="C198" s="22" t="s">
+      <c r="C198" s="24" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="22" t="s">
+      <c r="A199" s="23" t="s">
         <v>391</v>
       </c>
-      <c r="B199" s="22" t="s">
+      <c r="B199" s="23" t="s">
         <v>392</v>
       </c>
-      <c r="C199" s="22" t="s">
+      <c r="C199" s="23" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="B200" s="22" t="s">
+      <c r="B200" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="C200" s="22" t="s">
+      <c r="C200" s="23" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="22" t="s">
+      <c r="A201" s="23" t="s">
         <v>395</v>
       </c>
-      <c r="B201" s="22" t="s">
+      <c r="B201" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="C201" s="22" t="s">
+      <c r="C201" s="23" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="22" t="s">
+      <c r="A202" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="B202" s="22" t="s">
+      <c r="B202" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="C202" s="22" t="s">
+      <c r="C202" s="23" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="22" t="s">
+      <c r="A203" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="B203" s="22" t="s">
+      <c r="B203" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="C203" s="22" t="s">
+      <c r="C203" s="23" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204" s="22" t="s">
+      <c r="A204" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="B204" s="22" t="s">
+      <c r="B204" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="C204" s="22" t="s">
+      <c r="C204" s="23" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="22" t="s">
+      <c r="A205" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="B205" s="22" t="s">
+      <c r="B205" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="C205" s="22" t="s">
+      <c r="C205" s="23" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="22" t="s">
+      <c r="A206" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="B206" s="22" t="s">
+      <c r="B206" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="22" t="s">
+      <c r="C206" s="23" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="22" t="s">
+      <c r="A207" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="B207" s="22" t="s">
+      <c r="B207" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="22" t="s">
+      <c r="C207" s="23" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="22" t="s">
+      <c r="A208" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="B208" s="22" t="s">
+      <c r="B208" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="C208" s="22" t="s">
+      <c r="C208" s="23" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="22" t="s">
+      <c r="A209" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="B209" s="22" t="s">
+      <c r="B209" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="C209" s="22" t="s">
+      <c r="C209" s="23" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="22" t="s">
+      <c r="A210" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="B210" s="22" t="s">
+      <c r="B210" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="C210" s="22" t="s">
+      <c r="C210" s="23" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="20" t="s">
+      <c r="A211" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="B211" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="C211" s="20" t="s">
-        <v>185</v>
+      <c r="B211" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="C211" s="23" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="B212" s="20" t="s">
+      <c r="A212" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="B212" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C212" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="B213" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C213" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="B214" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C212" s="20" t="s">
+      <c r="C214" s="21" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="B213" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C213" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="20" t="s">
-        <v>418</v>
-      </c>
-      <c r="B214" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C214" s="20" t="s">
-        <v>191</v>
-      </c>
-    </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="B215" s="20" t="s">
+      <c r="A215" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="B215" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C215" s="20" t="s">
+      <c r="C215" s="21" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="B216" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C216" s="20" t="s">
-        <v>201</v>
+      <c r="A216" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="B216" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C216" s="21" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="B217" s="20" t="s">
+      <c r="A217" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C217" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="B218" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C218" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="B219" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C217" s="20" t="s">
+      <c r="C219" s="21" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="B218" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C218" s="20" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="B219" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="C219" s="20" t="s">
-        <v>203</v>
-      </c>
-    </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="B220" s="20" t="s">
+      <c r="A220" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="C220" s="20" t="s">
-        <v>425</v>
+      <c r="B220" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C220" s="21" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="20" t="s">
+      <c r="A221" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="B221" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C221" s="20" t="s">
-        <v>205</v>
+      <c r="B221" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="C221" s="21" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="B222" s="20" t="s">
+      <c r="A222" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="C222" s="20" t="s">
-        <v>428</v>
+      <c r="B222" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C222" s="21" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="22" t="s">
+      <c r="A223" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="B223" s="22" t="s">
+      <c r="B223" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="C223" s="22" t="s">
+      <c r="C223" s="21" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="22" t="s">
+      <c r="A224" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="B224" s="22" t="s">
+      <c r="B224" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="C224" s="22" t="s">
+      <c r="C224" s="23" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225" s="22" t="s">
+      <c r="A225" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="B225" s="22" t="s">
+      <c r="B225" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="C225" s="22" t="s">
+      <c r="C225" s="23" t="s">
         <v>434</v>
       </c>
     </row>
@@ -5521,95 +5534,95 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="22" t="s">
+      <c r="A227" s="24" t="s">
         <v>437</v>
       </c>
-      <c r="B227" s="22" t="s">
+      <c r="B227" s="24" t="s">
         <v>438</v>
       </c>
-      <c r="C227" s="22" t="s">
+      <c r="C227" s="24" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="22" t="s">
+      <c r="A228" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="B228" s="22" t="s">
+      <c r="B228" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="C228" s="22" t="s">
+      <c r="C228" s="23" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="22" t="s">
+      <c r="A229" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="B229" s="22" t="s">
+      <c r="B229" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="C229" s="22" t="s">
+      <c r="C229" s="23" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="22" t="s">
+      <c r="A230" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="B230" s="22" t="s">
+      <c r="B230" s="23" t="s">
         <v>444</v>
       </c>
-      <c r="C230" s="22" t="s">
+      <c r="C230" s="23" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="22" t="s">
+      <c r="A231" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="B231" s="22" t="s">
+      <c r="B231" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="C231" s="22" t="s">
+      <c r="C231" s="23" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="232" spans="1:3">
-      <c r="A232" s="22" t="s">
+      <c r="A232" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="B232" s="22" t="s">
+      <c r="B232" s="23" t="s">
         <v>448</v>
       </c>
-      <c r="C232" s="22" t="s">
+      <c r="C232" s="23" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233" s="22" t="s">
+      <c r="A233" s="23" t="s">
         <v>449</v>
       </c>
-      <c r="B233" s="22" t="s">
+      <c r="B233" s="23" t="s">
         <v>450</v>
       </c>
-      <c r="C233" s="22" t="s">
+      <c r="C233" s="23" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="6" t="s">
+      <c r="A234" s="23" t="s">
         <v>451</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="23" t="s">
         <v>452</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="23" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="6" t="s">
+      <c r="A235" s="7" t="s">
         <v>453</v>
       </c>
       <c r="B235" t="s">
@@ -5620,7 +5633,7 @@
       </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="6" t="s">
+      <c r="A236" s="7" t="s">
         <v>455</v>
       </c>
       <c r="B236" t="s">
@@ -5631,7 +5644,7 @@
       </c>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="7" t="s">
         <v>457</v>
       </c>
       <c r="B237" t="s">
@@ -5642,7 +5655,7 @@
       </c>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="7" t="s">
         <v>459</v>
       </c>
       <c r="B238" t="s">
@@ -5653,7 +5666,7 @@
       </c>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="7" t="s">
         <v>461</v>
       </c>
       <c r="B239" t="s">
@@ -5664,7 +5677,7 @@
       </c>
     </row>
     <row r="240" spans="1:3">
-      <c r="A240" s="6" t="s">
+      <c r="A240" s="7" t="s">
         <v>463</v>
       </c>
       <c r="B240" t="s">
@@ -5675,7 +5688,7 @@
       </c>
     </row>
     <row r="241" spans="1:3">
-      <c r="A241" s="6" t="s">
+      <c r="A241" s="7" t="s">
         <v>465</v>
       </c>
       <c r="B241" t="s">
@@ -5686,7 +5699,7 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" t="s">
+      <c r="A242" s="7" t="s">
         <v>467</v>
       </c>
       <c r="B242" t="s">
@@ -5774,7 +5787,7 @@
       </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250" s="6" t="s">
+      <c r="A250" t="s">
         <v>483</v>
       </c>
       <c r="B250" t="s">
@@ -5785,7 +5798,7 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="6" t="s">
+      <c r="A251" s="7" t="s">
         <v>485</v>
       </c>
       <c r="B251" t="s">
@@ -5796,7 +5809,7 @@
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="6" t="s">
+      <c r="A252" s="7" t="s">
         <v>487</v>
       </c>
       <c r="B252" t="s">
@@ -5807,7 +5820,7 @@
       </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="6" t="s">
+      <c r="A253" s="7" t="s">
         <v>489</v>
       </c>
       <c r="B253" t="s">
@@ -5817,85 +5830,85 @@
         <v>490</v>
       </c>
     </row>
-    <row r="254" s="4" customFormat="1" spans="1:3">
-      <c r="A254" s="10" t="s">
+    <row r="254" spans="1:3">
+      <c r="A254" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B254" s="8" t="s">
+      <c r="B254" t="s">
         <v>492</v>
       </c>
-      <c r="C254" s="8" t="s">
+      <c r="C254" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
-      <c r="A255" t="s">
+    <row r="255" s="4" customFormat="1" spans="1:3">
+      <c r="A255" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B255" s="6" t="s">
+      <c r="B255" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="C255" s="6" t="s">
+      <c r="C255" s="9" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="256" s="4" customFormat="1" spans="1:3">
-      <c r="A256" s="10" t="s">
+    <row r="256" spans="1:3">
+      <c r="A256" t="s">
         <v>495</v>
       </c>
-      <c r="B256" s="24" t="s">
+      <c r="B256" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="C256" s="24" t="s">
+      <c r="C256" s="7" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="257" s="4" customFormat="1" spans="1:3">
-      <c r="A257" s="10" t="s">
+      <c r="A257" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="25" t="s">
         <v>498</v>
       </c>
-      <c r="C257" s="8" t="s">
+      <c r="C257" s="25" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
-      <c r="A258" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B258" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>179</v>
+    <row r="258" s="4" customFormat="1" spans="1:3">
+      <c r="A258" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="B259" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="C259" s="8" t="s">
-        <v>500</v>
+      <c r="A259" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="6" t="s">
+      <c r="A260" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C260" s="9" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261" s="6" t="s">
+      <c r="A261" s="7" t="s">
         <v>503</v>
       </c>
       <c r="B261" t="s">
@@ -5906,227 +5919,235 @@
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B262" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>181</v>
+      <c r="A262" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="B262" t="s">
+        <v>506</v>
+      </c>
+      <c r="C262" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="B263" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>506</v>
+      <c r="A263" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="6" t="s">
+      <c r="A264" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="B264" s="8" t="s">
+      <c r="B264" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="C264" s="8" t="s">
+      <c r="C264" s="9" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B265" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>183</v>
+      <c r="A265" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="B266" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>510</v>
+      <c r="A266" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="6" t="s">
+      <c r="A267" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="B267" s="8" t="s">
+      <c r="B267" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="C267" s="8" t="s">
+      <c r="C267" s="9" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="6" t="s">
+      <c r="A268" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="B268" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="C268" s="24" t="s">
-        <v>308</v>
+      <c r="B268" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="B269" s="24" t="s">
+      <c r="A269" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="B269" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="C269" s="24" t="s">
+      <c r="C269" s="25" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="B270" s="24" t="s">
+      <c r="A270" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="C270" s="24" t="s">
-        <v>516</v>
+      <c r="B270" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="C270" s="25" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="6" t="s">
+      <c r="A271" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="B271" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="C271" s="24" t="s">
-        <v>312</v>
+      <c r="B271" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="C271" s="25" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="B272" s="24" t="s">
+      <c r="A272" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="C272" s="24" t="s">
-        <v>519</v>
+      <c r="B272" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C272" s="25" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="273" spans="1:3">
-      <c r="A273" s="6" t="s">
+      <c r="A273" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="B273" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="C273" s="24" t="s">
-        <v>316</v>
+      <c r="B273" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="C273" s="25" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="B274" s="24" t="s">
+      <c r="A274" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="C274" s="24" t="s">
-        <v>522</v>
+      <c r="B274" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C274" s="25" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275" s="6" t="s">
+      <c r="A275" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="B275" s="24" t="s">
+      <c r="B275" s="25" t="s">
         <v>524</v>
       </c>
-      <c r="C275" s="24" t="s">
+      <c r="C275" s="25" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="6" t="s">
+      <c r="A276" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="B276" s="24" t="s">
+      <c r="B276" s="25" t="s">
         <v>526</v>
       </c>
-      <c r="C276" s="24" t="s">
+      <c r="C276" s="25" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="6" t="s">
+      <c r="A277" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="B277" s="24" t="s">
+      <c r="B277" s="25" t="s">
         <v>528</v>
       </c>
-      <c r="C277" s="24" t="s">
+      <c r="C277" s="25" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="6" t="s">
+      <c r="A278" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C278" s="25" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="279" s="4" customFormat="1" spans="1:3">
-      <c r="A279" s="6" t="s">
+    <row r="279" spans="1:3">
+      <c r="A279" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="B279" t="s">
         <v>532</v>
       </c>
-      <c r="C279" s="25" t="s">
+      <c r="C279" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="26" t="s">
+    <row r="280" s="4" customFormat="1" spans="1:3">
+      <c r="A280" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="B280" s="24" t="s">
+      <c r="B280" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="C280" s="24" t="s">
+      <c r="C280" s="26" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281" s="26" t="s">
+      <c r="A281" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="25" t="s">
         <v>536</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C281" s="25" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
-      <c r="B283" s="27"/>
+    <row r="282" spans="1:3">
+      <c r="A282" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B282" t="s">
+        <v>538</v>
+      </c>
+      <c r="C282" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="284" spans="1:3">
       <c r="B284" s="27"/>
@@ -6134,15 +6155,18 @@
     <row r="285" spans="1:3">
       <c r="B285" s="27"/>
     </row>
+    <row r="286" spans="1:3">
+      <c r="B286" s="27"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B24" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
-    <hyperlink ref="C24" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
+    <hyperlink ref="B25" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
+    <hyperlink ref="C25" r:id="rId1" display="即时战略指挥攻略/攻略.txt"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C2 A4:B6" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="zh-Hans-CN" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="541">
   <si>
     <t>key</t>
   </si>
@@ -1847,6 +1847,12 @@
   </si>
   <si>
     <t>秒</t>
+  </si>
+  <si>
+    <t>Ping</t>
+  </si>
+  <si>
+    <t>乒</t>
   </si>
 </sst>
 </file>
@@ -6149,6 +6155,17 @@
         <v>538</v>
       </c>
     </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
+        <v>539</v>
+      </c>
+      <c r="B283" t="s">
+        <v>540</v>
+      </c>
+      <c r="C283" t="s">
+        <v>540</v>
+      </c>
+    </row>
     <row r="284" spans="1:3">
       <c r="B284" s="27"/>
     </row>
@@ -6166,7 +6183,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C2 A4:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/zh-Hans-CN.xlsx
+++ b/assets/翻译/zh-Hans-CN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="zh-Hans-CN" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,7 @@
     <t>Connecting</t>
   </si>
   <si>
-    <t>正在连接'</t>
+    <t>正在连接……</t>
   </si>
   <si>
     <t>ConnectError</t>
@@ -6183,7 +6183,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C2 A4:B6" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:B6 A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>